--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.67784905517228</v>
+        <v>2.222650471465495</v>
       </c>
       <c r="D2" t="n">
-        <v>12.55508841843516</v>
+        <v>2.040201867995713</v>
       </c>
       <c r="E2" t="n">
-        <v>4.422307326446582</v>
+        <v>0.7186249405475694</v>
       </c>
       <c r="F2" t="n">
-        <v>33.54708300430326</v>
+        <v>5.451400988199279</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.888715606346009</v>
+        <v>1.444416286031227</v>
       </c>
       <c r="D3" t="n">
-        <v>77.29037230075045</v>
+        <v>12.55968549887195</v>
       </c>
       <c r="E3" t="n">
-        <v>4.422307326446582</v>
+        <v>0.7186249405475694</v>
       </c>
       <c r="F3" t="n">
-        <v>33.54708300430326</v>
+        <v>5.451400988199279</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.86878531608595</v>
+        <v>0.4661776138639668</v>
       </c>
       <c r="D4" t="n">
-        <v>88.75579740886845</v>
+        <v>14.42281707894112</v>
       </c>
       <c r="E4" t="n">
-        <v>4.422307326446582</v>
+        <v>0.7186249405475694</v>
       </c>
       <c r="F4" t="n">
-        <v>33.54708300430326</v>
+        <v>5.451400988199279</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
